--- a/vse-loti/341101559/spec-341101559.xlsx
+++ b/vse-loti/341101559/spec-341101559.xlsx
@@ -1709,16 +1709,16 @@
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.155</v>
+        <v>1.282</v>
       </c>
       <c r="G42" s="4" t="n">
         <v>281000</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>1812903.23</v>
+        <v>219188.77</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>2211741.94</v>
+        <v>267410.3</v>
       </c>
     </row>
     <row r="43">
@@ -1744,16 +1744,16 @@
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>0.186</v>
+        <v>1.539</v>
       </c>
       <c r="G43" s="4" t="n">
         <v>337200</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>1812903.23</v>
+        <v>219103.31</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>2211741.94</v>
+        <v>267306.04</v>
       </c>
     </row>
     <row r="44">
@@ -1779,16 +1779,16 @@
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.257</v>
+        <v>2.127</v>
       </c>
       <c r="G44" s="4" t="n">
         <v>362863.68</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>1411920.93</v>
+        <v>170598.82</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>1722543.54</v>
+        <v>208130.55</v>
       </c>
     </row>
     <row r="45">
@@ -1814,16 +1814,16 @@
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>0.311</v>
+        <v>2.572</v>
       </c>
       <c r="G45" s="4" t="n">
         <v>438948</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>1411408.36</v>
+        <v>170664.07</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>1721918.2</v>
+        <v>208210.17</v>
       </c>
     </row>
     <row r="46">
@@ -1849,16 +1849,16 @@
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.381</v>
+        <v>3.152</v>
       </c>
       <c r="G46" s="4" t="n">
         <v>646187</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>1696028.87</v>
+        <v>205008.57</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>2069155.22</v>
+        <v>250110.45</v>
       </c>
     </row>
     <row r="47">
@@ -1884,16 +1884,16 @@
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>0.556</v>
+        <v>4.592</v>
       </c>
       <c r="G47" s="4" t="n">
         <v>887940</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>1597014.39</v>
+        <v>193366.72</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>1948357.55</v>
+        <v>235907.4</v>
       </c>
     </row>
     <row r="48">
@@ -1919,16 +1919,16 @@
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>1.329</v>
+        <v>10.98</v>
       </c>
       <c r="G48" s="4" t="n">
         <v>1297108</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>976003.01</v>
+        <v>118133.7</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>1190723.67</v>
+        <v>144123.11</v>
       </c>
     </row>
     <row r="49">
@@ -1954,16 +1954,16 @@
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>2.495</v>
+        <v>20.614</v>
       </c>
       <c r="G49" s="4" t="n">
         <v>4486119.45</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>1798043.87</v>
+        <v>217624.89</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>2193613.52</v>
+        <v>265502.36</v>
       </c>
     </row>
     <row r="50">
@@ -1989,16 +1989,16 @@
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>1.313</v>
+        <v>10.85</v>
       </c>
       <c r="G50" s="4" t="n">
         <v>2361115.5</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>1798260.09</v>
+        <v>217614.33</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>2193877.31</v>
+        <v>265489.48</v>
       </c>
     </row>
     <row r="51">
@@ -2024,16 +2024,16 @@
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>3.116</v>
+        <v>25.747</v>
       </c>
       <c r="G51" s="4" t="n">
         <v>6748672.5</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>2165812.74</v>
+        <v>262114.91</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>2642291.54</v>
+        <v>319780.19</v>
       </c>
     </row>
     <row r="52">
@@ -2059,16 +2059,16 @@
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>3.739</v>
+        <v>30.897</v>
       </c>
       <c r="G52" s="4" t="n">
         <v>8098407</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>2165928.59</v>
+        <v>262109.82</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>2642432.88</v>
+        <v>319773.98</v>
       </c>
     </row>
     <row r="53">
@@ -2094,16 +2094,16 @@
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>0.056</v>
+        <v>0.462</v>
       </c>
       <c r="G53" s="4" t="n">
         <v>128067</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>2286910.71</v>
+        <v>277201.3</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>2790031.07</v>
+        <v>338185.58</v>
       </c>
     </row>
     <row r="54">
@@ -2129,16 +2129,16 @@
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>11.129</v>
+        <v>91.96599999999999</v>
       </c>
       <c r="G54" s="4" t="n">
         <v>25010378.18</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>2247315.86</v>
+        <v>271952.44</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>2741725.35</v>
+        <v>331781.98</v>
       </c>
     </row>
     <row r="55">
@@ -2164,16 +2164,16 @@
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>4.455</v>
+        <v>36.816</v>
       </c>
       <c r="G55" s="4" t="n">
         <v>10012161</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>2247398.65</v>
+        <v>271951.35</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>2741826.36</v>
+        <v>331780.65</v>
       </c>
     </row>
     <row r="56">
@@ -2199,16 +2199,16 @@
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>7.242</v>
+        <v>59.857</v>
       </c>
       <c r="G56" s="4" t="n">
         <v>16382058.1</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>2262090.32</v>
+        <v>273686.59</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>2759750.19</v>
+        <v>333897.64</v>
       </c>
     </row>
     <row r="57">
@@ -2234,16 +2234,16 @@
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>3.82</v>
+        <v>31.57</v>
       </c>
       <c r="G57" s="4" t="n">
         <v>8640326</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>2261865.45</v>
+        <v>273687.87</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>2759475.84</v>
+        <v>333899.2</v>
       </c>
     </row>
     <row r="58">
@@ -2269,16 +2269,16 @@
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>0.06</v>
+        <v>0.497</v>
       </c>
       <c r="G58" s="4" t="n">
         <v>116683.7</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>1944728.33</v>
+        <v>234776.06</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>2372568.57</v>
+        <v>286426.79</v>
       </c>
     </row>
     <row r="59">
@@ -2304,16 +2304,16 @@
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>2.178</v>
+        <v>18.004</v>
       </c>
       <c r="G59" s="4" t="n">
         <v>3869197</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>1776490.82</v>
+        <v>214907.63</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>2167318.8</v>
+        <v>262187.31</v>
       </c>
     </row>
     <row r="60">
@@ -2339,16 +2339,16 @@
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>0.081</v>
+        <v>0.67</v>
       </c>
       <c r="G60" s="4" t="n">
         <v>160404</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>1980296.3</v>
+        <v>239408.96</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>2415961.48</v>
+        <v>292078.93</v>
       </c>
     </row>
     <row r="61">
@@ -2693,16 +2693,16 @@
         </is>
       </c>
       <c r="F72" s="5" t="n">
-        <v>0.056</v>
+        <v>0.466</v>
       </c>
       <c r="G72" s="4" t="n">
         <v>277081.2</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>4947878.57</v>
+        <v>594594.85</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>6036411.86</v>
+        <v>725405.72</v>
       </c>
     </row>
     <row r="73">
@@ -2728,16 +2728,16 @@
         </is>
       </c>
       <c r="F73" s="5" t="n">
-        <v>0.368</v>
+        <v>3.044</v>
       </c>
       <c r="G73" s="4" t="n">
         <v>1461797.94</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>3972277.01</v>
+        <v>480222.71</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>4846177.95</v>
+        <v>585871.71</v>
       </c>
     </row>
     <row r="74">
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="F74" s="8" t="n">
-        <v>43.283</v>
+        <v>357.704</v>
       </c>
       <c r="G74" s="9" t="n">
         <v>119899308.87</v>

--- a/vse-loti/341101559/spec-341101559.xlsx
+++ b/vse-loti/341101559/spec-341101559.xlsx
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -97,6 +97,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -465,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I80"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2773,19 +2776,26 @@
         <v>146277156.81</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="10" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>НДС 22 %, ставка из документа: "ь ответственного хранения за 1 м2 составляет 27,10 руб., в том числе НДС 22 % 4,89 руб." — Проект договора_ГоГРЭС.txt; суммы источника указаны без НДС: "Цена за единицу (предложение участника) без НДС" — 226110_297.26.00328_КОММ.txt. «без НДС» — сумма из документа, «с НДС» = сумма × 1,22.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="11" t="inlineStr">
         <is>
           <t>Источник: 226110_297.26.00328_КОММ.xlsx
 226110_560.26.00744_КОММ.xlsx</t>
         </is>
       </c>
     </row>
-    <row r="79"/>
     <row r="80"/>
+    <row r="81"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A78:B80"/>
+    <mergeCell ref="A79:B81"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vse-loti/341101559/spec-341101559.xlsx
+++ b/vse-loti/341101559/spec-341101559.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -480,6 +480,7 @@
     <col width="20.28515625" customWidth="1" min="7" max="7"/>
     <col width="18.85546875" customWidth="1" min="8" max="8"/>
     <col width="16.42578125" customWidth="1" min="9" max="9"/>
+    <col width="18.85546875" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -515,17 +516,22 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Цена за т (без НДС)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Стоимость (без НДС)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Цена за т (без НДС)</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Стоимость (с НДС)</t>
         </is>
       </c>
     </row>
@@ -552,11 +558,14 @@
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" s="4" t="n">
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" s="4" t="n">
         <v>43763.2</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" s="4" t="n">
+        <v>53391.1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -581,11 +590,14 @@
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" s="4" t="n">
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" s="4" t="n">
         <v>109408</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" s="4" t="n">
+        <v>133477.76</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -610,11 +622,14 @@
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" s="4" t="n">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" s="4" t="n">
         <v>53166.4</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" s="4" t="n">
+        <v>64863.01</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -639,11 +654,14 @@
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" s="4" t="n">
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" s="4" t="n">
         <v>265832</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" s="4" t="n">
+        <v>324315.04</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -668,11 +686,14 @@
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" s="4" t="n">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" s="4" t="n">
         <v>187257.18</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" s="4" t="n">
+        <v>228453.76</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -697,11 +718,14 @@
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" s="4" t="n">
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" s="4" t="n">
         <v>366678.06</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" s="4" t="n">
+        <v>447347.23</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -726,11 +750,14 @@
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" s="4" t="n">
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" s="4" t="n">
         <v>619859.88</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" s="4" t="n">
+        <v>756229.05</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -755,11 +782,14 @@
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" s="4" t="n">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" s="4" t="n">
         <v>647648.28</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" s="4" t="n">
+        <v>790130.9</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -784,11 +814,14 @@
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" s="4" t="n">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" s="4" t="n">
         <v>971472.42</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" s="4" t="n">
+        <v>1185196.35</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -813,11 +846,14 @@
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" s="4" t="n">
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" s="4" t="n">
         <v>353135.36</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" s="4" t="n">
+        <v>430825.14</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -842,11 +878,14 @@
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" s="4" t="n">
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" s="4" t="n">
         <v>1765676.8</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" s="4" t="n">
+        <v>2154125.7</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -871,11 +910,14 @@
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" s="4" t="n">
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" s="4" t="n">
         <v>69442.10000000001</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" s="4" t="n">
+        <v>84719.36</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -900,11 +942,14 @@
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" s="4" t="n">
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" s="4" t="n">
         <v>1992152</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" s="4" t="n">
+        <v>2430425.44</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -929,11 +974,14 @@
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" s="4" t="n">
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" s="4" t="n">
         <v>1159819.68</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" s="4" t="n">
+        <v>1414980.01</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -958,11 +1006,14 @@
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" s="4" t="n">
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" s="4" t="n">
         <v>1739729.52</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" s="4" t="n">
+        <v>2122470.01</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -987,11 +1038,14 @@
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" s="4" t="n">
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" s="4" t="n">
         <v>81437.60000000001</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" s="4" t="n">
+        <v>99353.87</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1016,11 +1070,14 @@
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" s="4" t="n">
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" s="4" t="n">
         <v>2103807.18</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" s="4" t="n">
+        <v>2566644.76</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1045,11 +1102,14 @@
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" s="4" t="n">
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" s="4" t="n">
         <v>93975.10000000001</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" s="4" t="n">
+        <v>114649.62</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1074,11 +1134,14 @@
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" s="4" t="n">
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" s="4" t="n">
         <v>12331.9</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" s="4" t="n">
+        <v>15044.92</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1103,11 +1166,14 @@
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
-      <c r="G21" s="4" t="n">
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" s="4" t="n">
         <v>73991.39999999999</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" s="4" t="n">
+        <v>90269.50999999999</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -1132,11 +1198,14 @@
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
-      <c r="G22" s="4" t="n">
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" s="4" t="n">
         <v>61659.5</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" s="4" t="n">
+        <v>75224.59</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -1161,11 +1230,14 @@
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
-      <c r="G23" s="4" t="n">
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" s="4" t="n">
         <v>25023.84</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" s="4" t="n">
+        <v>30529.08</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1190,11 +1262,14 @@
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" s="4" t="n">
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" s="4" t="n">
         <v>125119.2</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" s="4" t="n">
+        <v>152645.42</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -1219,11 +1294,14 @@
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" s="4" t="n">
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" s="4" t="n">
         <v>253353</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" s="4" t="n">
+        <v>309090.66</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -1248,11 +1326,14 @@
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
-      <c r="G26" s="4" t="n">
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" s="4" t="n">
         <v>235096.8</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" s="4" t="n">
+        <v>286818.1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -1277,11 +1358,14 @@
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
-      <c r="G27" s="4" t="n">
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" s="4" t="n">
         <v>296185.14</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" s="4" t="n">
+        <v>361345.87</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -1306,11 +1390,14 @@
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
-      <c r="G28" s="4" t="n">
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" s="4" t="n">
         <v>463650.42</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" s="4" t="n">
+        <v>565653.51</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -1335,11 +1422,14 @@
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" s="4" t="n">
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" s="4" t="n">
         <v>546750.5600000001</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" s="4" t="n">
+        <v>667035.6800000001</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -1364,11 +1454,14 @@
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
-      <c r="G30" s="4" t="n">
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" s="4" t="n">
         <v>820125.84</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" s="4" t="n">
+        <v>1000553.52</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -1393,11 +1486,14 @@
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
-      <c r="G31" s="4" t="n">
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" s="4" t="n">
         <v>6687.6</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" s="4" t="n">
+        <v>8158.87</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -1422,11 +1518,14 @@
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
-      <c r="G32" s="4" t="n">
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" s="4" t="n">
         <v>33438</v>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" s="4" t="n">
+        <v>40794.36</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -1451,11 +1550,14 @@
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
-      <c r="G33" s="4" t="n">
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" s="4" t="n">
         <v>1245825.78</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" s="4" t="n">
+        <v>1519907.45</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -1480,11 +1582,14 @@
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
-      <c r="G34" s="4" t="n">
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" s="4" t="n">
         <v>1245825.78</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" s="4" t="n">
+        <v>1519907.45</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -1509,11 +1614,14 @@
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
-      <c r="G35" s="4" t="n">
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" s="4" t="n">
         <v>3043727.1</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" s="4" t="n">
+        <v>3713347.06</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -1538,11 +1646,14 @@
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
-      <c r="G36" s="4" t="n">
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" s="4" t="n">
         <v>1826236.26</v>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" s="4" t="n">
+        <v>2228008.24</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -1567,11 +1678,14 @@
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" s="4" t="n">
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" s="4" t="n">
         <v>9673.360000000001</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" s="4" t="n">
+        <v>11801.5</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -1596,11 +1710,14 @@
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
-      <c r="G38" s="4" t="n">
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" s="4" t="n">
         <v>48366.8</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" s="4" t="n">
+        <v>59007.5</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -1625,11 +1742,14 @@
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
-      <c r="G39" s="4" t="n">
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" s="4" t="n">
         <v>1493116.04</v>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" s="4" t="n">
+        <v>1821601.57</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -1654,11 +1774,14 @@
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" s="4" t="n">
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" s="4" t="n">
         <v>11113.48</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" s="4" t="n">
+        <v>13558.45</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -1683,11 +1806,14 @@
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" s="4" t="n">
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" s="4" t="n">
         <v>55567.4</v>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" s="4" t="n">
+        <v>67792.23</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -1715,13 +1841,16 @@
         <v>1.282</v>
       </c>
       <c r="G42" s="4" t="n">
+        <v>219188.77</v>
+      </c>
+      <c r="H42" s="4" t="n">
         <v>281000</v>
-      </c>
-      <c r="H42" s="4" t="n">
-        <v>219188.77</v>
       </c>
       <c r="I42" s="4" t="n">
         <v>267410.3</v>
+      </c>
+      <c r="J42" s="4" t="n">
+        <v>342820</v>
       </c>
     </row>
     <row r="43">
@@ -1750,13 +1879,16 @@
         <v>1.539</v>
       </c>
       <c r="G43" s="4" t="n">
+        <v>219103.31</v>
+      </c>
+      <c r="H43" s="4" t="n">
         <v>337200</v>
-      </c>
-      <c r="H43" s="4" t="n">
-        <v>219103.31</v>
       </c>
       <c r="I43" s="4" t="n">
         <v>267306.04</v>
+      </c>
+      <c r="J43" s="4" t="n">
+        <v>411384</v>
       </c>
     </row>
     <row r="44">
@@ -1785,13 +1917,16 @@
         <v>2.127</v>
       </c>
       <c r="G44" s="4" t="n">
+        <v>170598.82</v>
+      </c>
+      <c r="H44" s="4" t="n">
         <v>362863.68</v>
-      </c>
-      <c r="H44" s="4" t="n">
-        <v>170598.82</v>
       </c>
       <c r="I44" s="4" t="n">
         <v>208130.55</v>
+      </c>
+      <c r="J44" s="4" t="n">
+        <v>442693.69</v>
       </c>
     </row>
     <row r="45">
@@ -1820,13 +1955,16 @@
         <v>2.572</v>
       </c>
       <c r="G45" s="4" t="n">
+        <v>170664.07</v>
+      </c>
+      <c r="H45" s="4" t="n">
         <v>438948</v>
-      </c>
-      <c r="H45" s="4" t="n">
-        <v>170664.07</v>
       </c>
       <c r="I45" s="4" t="n">
         <v>208210.17</v>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v>535516.5600000001</v>
       </c>
     </row>
     <row r="46">
@@ -1855,13 +1993,16 @@
         <v>3.152</v>
       </c>
       <c r="G46" s="4" t="n">
+        <v>205008.57</v>
+      </c>
+      <c r="H46" s="4" t="n">
         <v>646187</v>
-      </c>
-      <c r="H46" s="4" t="n">
-        <v>205008.57</v>
       </c>
       <c r="I46" s="4" t="n">
         <v>250110.45</v>
+      </c>
+      <c r="J46" s="4" t="n">
+        <v>788348.14</v>
       </c>
     </row>
     <row r="47">
@@ -1890,13 +2031,16 @@
         <v>4.592</v>
       </c>
       <c r="G47" s="4" t="n">
+        <v>193366.72</v>
+      </c>
+      <c r="H47" s="4" t="n">
         <v>887940</v>
-      </c>
-      <c r="H47" s="4" t="n">
-        <v>193366.72</v>
       </c>
       <c r="I47" s="4" t="n">
         <v>235907.4</v>
+      </c>
+      <c r="J47" s="4" t="n">
+        <v>1083286.8</v>
       </c>
     </row>
     <row r="48">
@@ -1925,13 +2069,16 @@
         <v>10.98</v>
       </c>
       <c r="G48" s="4" t="n">
+        <v>118133.7</v>
+      </c>
+      <c r="H48" s="4" t="n">
         <v>1297108</v>
-      </c>
-      <c r="H48" s="4" t="n">
-        <v>118133.7</v>
       </c>
       <c r="I48" s="4" t="n">
         <v>144123.11</v>
+      </c>
+      <c r="J48" s="4" t="n">
+        <v>1582471.76</v>
       </c>
     </row>
     <row r="49">
@@ -1960,13 +2107,16 @@
         <v>20.614</v>
       </c>
       <c r="G49" s="4" t="n">
+        <v>217624.89</v>
+      </c>
+      <c r="H49" s="4" t="n">
         <v>4486119.45</v>
-      </c>
-      <c r="H49" s="4" t="n">
-        <v>217624.89</v>
       </c>
       <c r="I49" s="4" t="n">
         <v>265502.36</v>
+      </c>
+      <c r="J49" s="4" t="n">
+        <v>5473065.73</v>
       </c>
     </row>
     <row r="50">
@@ -1995,13 +2145,16 @@
         <v>10.85</v>
       </c>
       <c r="G50" s="4" t="n">
+        <v>217614.33</v>
+      </c>
+      <c r="H50" s="4" t="n">
         <v>2361115.5</v>
-      </c>
-      <c r="H50" s="4" t="n">
-        <v>217614.33</v>
       </c>
       <c r="I50" s="4" t="n">
         <v>265489.48</v>
+      </c>
+      <c r="J50" s="4" t="n">
+        <v>2880560.91</v>
       </c>
     </row>
     <row r="51">
@@ -2030,13 +2183,16 @@
         <v>25.747</v>
       </c>
       <c r="G51" s="4" t="n">
+        <v>262114.91</v>
+      </c>
+      <c r="H51" s="4" t="n">
         <v>6748672.5</v>
-      </c>
-      <c r="H51" s="4" t="n">
-        <v>262114.91</v>
       </c>
       <c r="I51" s="4" t="n">
         <v>319780.19</v>
+      </c>
+      <c r="J51" s="4" t="n">
+        <v>8233380.45</v>
       </c>
     </row>
     <row r="52">
@@ -2065,13 +2221,16 @@
         <v>30.897</v>
       </c>
       <c r="G52" s="4" t="n">
+        <v>262109.82</v>
+      </c>
+      <c r="H52" s="4" t="n">
         <v>8098407</v>
-      </c>
-      <c r="H52" s="4" t="n">
-        <v>262109.82</v>
       </c>
       <c r="I52" s="4" t="n">
         <v>319773.98</v>
+      </c>
+      <c r="J52" s="4" t="n">
+        <v>9880056.539999999</v>
       </c>
     </row>
     <row r="53">
@@ -2100,13 +2259,16 @@
         <v>0.462</v>
       </c>
       <c r="G53" s="4" t="n">
+        <v>277201.3</v>
+      </c>
+      <c r="H53" s="4" t="n">
         <v>128067</v>
-      </c>
-      <c r="H53" s="4" t="n">
-        <v>277201.3</v>
       </c>
       <c r="I53" s="4" t="n">
         <v>338185.58</v>
+      </c>
+      <c r="J53" s="4" t="n">
+        <v>156241.74</v>
       </c>
     </row>
     <row r="54">
@@ -2135,13 +2297,16 @@
         <v>91.96599999999999</v>
       </c>
       <c r="G54" s="4" t="n">
+        <v>271952.44</v>
+      </c>
+      <c r="H54" s="4" t="n">
         <v>25010378.18</v>
-      </c>
-      <c r="H54" s="4" t="n">
-        <v>271952.44</v>
       </c>
       <c r="I54" s="4" t="n">
         <v>331781.98</v>
+      </c>
+      <c r="J54" s="4" t="n">
+        <v>30512661.38</v>
       </c>
     </row>
     <row r="55">
@@ -2170,13 +2335,16 @@
         <v>36.816</v>
       </c>
       <c r="G55" s="4" t="n">
+        <v>271951.35</v>
+      </c>
+      <c r="H55" s="4" t="n">
         <v>10012161</v>
-      </c>
-      <c r="H55" s="4" t="n">
-        <v>271951.35</v>
       </c>
       <c r="I55" s="4" t="n">
         <v>331780.65</v>
+      </c>
+      <c r="J55" s="4" t="n">
+        <v>12214836.42</v>
       </c>
     </row>
     <row r="56">
@@ -2205,13 +2373,16 @@
         <v>59.857</v>
       </c>
       <c r="G56" s="4" t="n">
+        <v>273686.59</v>
+      </c>
+      <c r="H56" s="4" t="n">
         <v>16382058.1</v>
-      </c>
-      <c r="H56" s="4" t="n">
-        <v>273686.59</v>
       </c>
       <c r="I56" s="4" t="n">
         <v>333897.64</v>
+      </c>
+      <c r="J56" s="4" t="n">
+        <v>19986110.88</v>
       </c>
     </row>
     <row r="57">
@@ -2240,13 +2411,16 @@
         <v>31.57</v>
       </c>
       <c r="G57" s="4" t="n">
+        <v>273687.87</v>
+      </c>
+      <c r="H57" s="4" t="n">
         <v>8640326</v>
-      </c>
-      <c r="H57" s="4" t="n">
-        <v>273687.87</v>
       </c>
       <c r="I57" s="4" t="n">
         <v>333899.2</v>
+      </c>
+      <c r="J57" s="4" t="n">
+        <v>10541197.72</v>
       </c>
     </row>
     <row r="58">
@@ -2275,13 +2449,16 @@
         <v>0.497</v>
       </c>
       <c r="G58" s="4" t="n">
+        <v>234776.06</v>
+      </c>
+      <c r="H58" s="4" t="n">
         <v>116683.7</v>
-      </c>
-      <c r="H58" s="4" t="n">
-        <v>234776.06</v>
       </c>
       <c r="I58" s="4" t="n">
         <v>286426.79</v>
+      </c>
+      <c r="J58" s="4" t="n">
+        <v>142354.11</v>
       </c>
     </row>
     <row r="59">
@@ -2310,13 +2487,16 @@
         <v>18.004</v>
       </c>
       <c r="G59" s="4" t="n">
+        <v>214907.63</v>
+      </c>
+      <c r="H59" s="4" t="n">
         <v>3869197</v>
-      </c>
-      <c r="H59" s="4" t="n">
-        <v>214907.63</v>
       </c>
       <c r="I59" s="4" t="n">
         <v>262187.31</v>
+      </c>
+      <c r="J59" s="4" t="n">
+        <v>4720420.34</v>
       </c>
     </row>
     <row r="60">
@@ -2345,13 +2525,16 @@
         <v>0.67</v>
       </c>
       <c r="G60" s="4" t="n">
+        <v>239408.96</v>
+      </c>
+      <c r="H60" s="4" t="n">
         <v>160404</v>
-      </c>
-      <c r="H60" s="4" t="n">
-        <v>239408.96</v>
       </c>
       <c r="I60" s="4" t="n">
         <v>292078.93</v>
+      </c>
+      <c r="J60" s="4" t="n">
+        <v>195692.88</v>
       </c>
     </row>
     <row r="61">
@@ -2377,11 +2560,14 @@
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
-      <c r="G61" s="4" t="n">
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" s="4" t="n">
         <v>239638.32</v>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" s="4" t="n">
+        <v>292358.75</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -2406,11 +2592,14 @@
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
-      <c r="G62" s="4" t="n">
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" s="4" t="n">
         <v>119819.16</v>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" s="4" t="n">
+        <v>146179.38</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -2435,11 +2624,14 @@
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" s="4" t="n">
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" s="4" t="n">
         <v>296672.16</v>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" s="4" t="n">
+        <v>361940.04</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -2464,11 +2656,14 @@
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
-      <c r="G64" s="4" t="n">
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" s="4" t="n">
         <v>296672.16</v>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" s="4" t="n">
+        <v>361940.04</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -2493,11 +2688,14 @@
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
-      <c r="G65" s="4" t="n">
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" s="4" t="n">
         <v>849204.2</v>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" s="4" t="n">
+        <v>1036029.12</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -2522,11 +2720,14 @@
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
-      <c r="G66" s="4" t="n">
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" s="4" t="n">
         <v>339681.68</v>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" s="4" t="n">
+        <v>414411.65</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -2551,11 +2752,14 @@
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
-      <c r="G67" s="4" t="n">
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" s="4" t="n">
         <v>192033.22</v>
       </c>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" s="4" t="n">
+        <v>234280.53</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -2580,11 +2784,14 @@
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
-      <c r="G68" s="4" t="n">
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" s="4" t="n">
         <v>384066.44</v>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" s="4" t="n">
+        <v>468561.06</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
@@ -2609,11 +2816,14 @@
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
-      <c r="G69" s="4" t="n">
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" s="4" t="n">
         <v>514517.84</v>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" s="4" t="n">
+        <v>627711.76</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -2638,11 +2848,14 @@
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
-      <c r="G70" s="4" t="n">
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" s="4" t="n">
         <v>11921.76</v>
       </c>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" s="4" t="n">
+        <v>14544.55</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -2667,11 +2880,14 @@
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
-      <c r="G71" s="4" t="n">
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" s="4" t="n">
         <v>94240.72</v>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" s="4" t="n">
+        <v>114973.68</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -2699,13 +2915,16 @@
         <v>0.466</v>
       </c>
       <c r="G72" s="4" t="n">
+        <v>594594.85</v>
+      </c>
+      <c r="H72" s="4" t="n">
         <v>277081.2</v>
-      </c>
-      <c r="H72" s="4" t="n">
-        <v>594594.85</v>
       </c>
       <c r="I72" s="4" t="n">
         <v>725405.72</v>
+      </c>
+      <c r="J72" s="4" t="n">
+        <v>338039.06</v>
       </c>
     </row>
     <row r="73">
@@ -2734,14 +2953,17 @@
         <v>3.044</v>
       </c>
       <c r="G73" s="4" t="n">
+        <v>480222.71</v>
+      </c>
+      <c r="H73" s="4" t="n">
         <v>1461797.94</v>
-      </c>
-      <c r="H73" s="4" t="n">
-        <v>480222.71</v>
       </c>
       <c r="I73" s="4" t="n">
         <v>585871.71</v>
       </c>
+      <c r="J73" s="4" t="n">
+        <v>1783393.49</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
@@ -2753,7 +2975,16 @@
         <v>357.704</v>
       </c>
       <c r="G74" s="9" t="n">
+        <v>335191.41</v>
+      </c>
+      <c r="H74" s="9" t="n">
         <v>119899308.87</v>
+      </c>
+      <c r="I74" s="9" t="n">
+        <v>408933.52</v>
+      </c>
+      <c r="J74" s="9" t="n">
+        <v>146277156.82</v>
       </c>
     </row>
     <row r="75">
@@ -2762,7 +2993,7 @@
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="G75" s="9" t="n">
+      <c r="H75" s="9" t="n">
         <v>119899308.864</v>
       </c>
     </row>
@@ -2772,7 +3003,7 @@
           <t>НМЦК с НДС 22%:</t>
         </is>
       </c>
-      <c r="F76" s="9" t="n">
+      <c r="J76" s="9" t="n">
         <v>146277156.81</v>
       </c>
     </row>
